--- a/artfynd/A 7941-2024 artfynd.xlsx
+++ b/artfynd/A 7941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,62 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99837825</v>
+        <v>82862003</v>
       </c>
       <c r="B2" t="n">
-        <v>55511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102932</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skruvshult, Skruvshult-Forsa  Mönsterås, Sm</t>
+          <t>Skruvshult södra, Emsfors, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587561.6271840788</v>
+        <v>587529</v>
       </c>
       <c r="R2" t="n">
-        <v>6333465.098177617</v>
+        <v>6333593</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-04-12</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett 40-tal hanar och honor på det översvämmade fältet.</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +782,366 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Leon Axelsson Widén</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Leon Axelsson Widén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>99123474</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kring Fågelsjö, SO om Emsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>587548</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6333595</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-07-05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>FLD0055 (Calluna Ab) nattskärreinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Urban Rundström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>99123482</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kring Fågelsjö, SO om Emsfors, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587485</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6333535</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-06-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-06-20</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>FLD0055 (Calluna Ab) nattskärreinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Josefina Pehrson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99837825</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57105</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skruvshult, Skruvshult-Forsa  Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>587562</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6333465</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ett 40-tal hanar och honor på det översvämmade fältet.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Elisabeth Shahin Vidmark</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Elisabeth Shahin Vidmark</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7941-2024 artfynd.xlsx
+++ b/artfynd/A 7941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82862003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -912,6 +922,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123474</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1028,6 +1043,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99123482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1142,8 +1162,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99837825</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>